--- a/main/ig/StructureDefinition-cdl-bundle-creation-note.xlsx
+++ b/main/ig/StructureDefinition-cdl-bundle-creation-note.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.0</t>
+    <t>3.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T07:40:33+00:00</t>
+    <t>2026-07-21T12:38:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
@@ -111,7 +111,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Bundle</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Bundle|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -873,7 +873,7 @@
     <t>Bundle.entry:DocumentReference.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">DocumentReference {https://interop.esante.gouv.fr/ig/fhir/cdl/StructureDefinition/cdl-document-reference}
+    <t xml:space="preserve">DocumentReference {https://interop.esante.gouv.fr/ig/fhir/cdl/StructureDefinition/cdl-document-reference|3.0.1}
 </t>
   </si>
   <si>
@@ -998,7 +998,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Patient {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient}
+    <t xml:space="preserve">Patient {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.0.1}
 </t>
   </si>
   <si>
@@ -1117,7 +1117,7 @@
     <t>Bundle.entry:Practitioner.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Practitioner {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner}
+    <t xml:space="preserve">Practitioner {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|1.0.1}
 </t>
   </si>
   <si>
@@ -1232,7 +1232,7 @@
     <t>Bundle.entry:PractitionerRole.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">PractitionerRole {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole}
+    <t xml:space="preserve">PractitionerRole {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole|1.0.1}
 </t>
   </si>
   <si>
@@ -1341,7 +1341,7 @@
     <t>Bundle.entry:Organization.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Organization {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization}
+    <t xml:space="preserve">Organization {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.0.1}
 </t>
   </si>
   <si>
@@ -1456,7 +1456,7 @@
     <t>Bundle.entry:RelatedPerson.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">RelatedPerson {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person}
+    <t xml:space="preserve">RelatedPerson {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|2.0.1}
 </t>
   </si>
   <si>
@@ -1978,7 +1978,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="85.6328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="90.16015625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/main/ig/StructureDefinition-cdl-bundle-creation-note.xlsx
+++ b/main/ig/StructureDefinition-cdl-bundle-creation-note.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T12:38:43+00:00</t>
+    <t>2026-07-21T13:00:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-cdl-bundle-creation-note.xlsx
+++ b/main/ig/StructureDefinition-cdl-bundle-creation-note.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T13:00:31+00:00</t>
+    <t>2026-07-21T13:21:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-cdl-bundle-creation-note.xlsx
+++ b/main/ig/StructureDefinition-cdl-bundle-creation-note.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T13:21:42+00:00</t>
+    <t>2026-07-21T13:26:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
